--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T01:04:27+00:00</t>
+    <t>2026-10-19T02:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -372,10 +372,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen material</t>
-  </si>
-  <si>
-    <t>Examined specimen material. The specimen type is represented via the specimen material and not via pre-coordinated investigation codes.</t>
+    <t>Specimen</t>
+  </si>
+  <si>
+    <t>Specimen examined. The specimen type is represented via the specimen and not via pre-coordinated investigation codes.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchung.Probenmaterial</t>
@@ -813,7 +813,7 @@
     <t>Susceptibility</t>
   </si>
   <si>
-    <t>Result of phenotypic resistance testing of a pathogen against an antimicrobial substance with reference to a norm system.</t>
+    <t>Result of phenotypic resistance testing of a pathogen against an antimicrobial substance with reference to an interpretive standard (e.g. EUCAST, CLSI).</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Empfindlichkeit.id</t>
@@ -871,7 +871,7 @@
     <t>Norm</t>
   </si>
   <si>
-    <t>Norm system including version on whose breakpoints the category is based, e.g. EUCAST or CLSI.</t>
+    <t>Interpretive standard including version on whose breakpoints the category is based, e.g. EUCAST or CLSI.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Bestimmung</t>
@@ -1060,7 +1060,7 @@
     <t>mii-lm-mikrobio-untersuchungsarten.WeitereEigenschaften.ResistenzmechanismenDeterminanten</t>
   </si>
   <si>
-    <t>Resistance mechanism</t>
+    <t>Resistance mechanisms / determinants</t>
   </si>
   <si>
     <t>Detection of resistance genes or resistance mutations as an indication of a specific resistance mechanism.</t>
@@ -1123,7 +1123,7 @@
     <t>Predicted susceptibility</t>
   </si>
   <si>
-    <t>Expected susceptibility or resistance to antimicrobial substances derived from genotypic detections.</t>
+    <t>Predicted susceptibility or resistance to antimicrobial substances derived from genotypic detections.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.WeitereEigenschaften.VoraussichtlicheEmpfindlichkeit.id</t>
@@ -1144,7 +1144,7 @@
     <t>mii-lm-mikrobio-untersuchungsarten.WeitereEigenschaften.VoraussichtlicheEmpfindlichkeit.Ergebnis</t>
   </si>
   <si>
-    <t>Expected susceptibility or resistance.</t>
+    <t>Predicted susceptibility or resistance.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.WeitereEigenschaften.ResistenzkategorieStatus</t>
@@ -1249,7 +1249,7 @@
     <t>mii-lm-mikrobio-untersuchungsarten.QuantitativeTests.AntigenAntikoerperQuantitativ</t>
   </si>
   <si>
-    <t>Antigen antibody tests</t>
+    <t>Antigen/antibody quantitative</t>
   </si>
   <si>
     <t>Quantitative measurement of pathogen-specific antigens or antibodies by immunological procedures.</t>

--- a/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/review/2027.0.0-ballot2-en/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T02:33:36+00:00</t>
+    <t>2026-10-19T02:49:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
